--- a/Google_Ads_Campaign_1.xlsx
+++ b/Google_Ads_Campaign_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="e:\react project\kevin-graham-profile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F366A6-674F-4E60-BC47-522D053275D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB412D83-9484-43BD-A383-2A638163F178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" firstSheet="3" activeTab="5" xr2:uid="{D76E1C49-027D-4506-86F0-0DA797BAD358}"/>
+    <workbookView xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" firstSheet="3" activeTab="6" xr2:uid="{D76E1C49-027D-4506-86F0-0DA797BAD358}"/>
   </bookViews>
   <sheets>
     <sheet name="Google Ads Upload" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Assets - Sitelinks" sheetId="4" r:id="rId4"/>
     <sheet name="Assets - Callouts &amp; Snippets" sheetId="5" r:id="rId5"/>
     <sheet name="Char Count Check" sheetId="6" r:id="rId6"/>
+    <sheet name="Negative Keywords" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="548">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3099" uniqueCount="858">
   <si>
     <t>Campaign</t>
   </si>
@@ -1683,6 +1684,936 @@
   </si>
   <si>
     <t>Debt Rescheduling Advisory</t>
+  </si>
+  <si>
+    <t>Reason / Notes</t>
+  </si>
+  <si>
+    <t>ACCOUNT-LEVEL — Block across ALL campaigns</t>
+  </si>
+  <si>
+    <t>free money</t>
+  </si>
+  <si>
+    <t>No free handouts — Kevin charges advisory fees</t>
+  </si>
+  <si>
+    <t>payday loan</t>
+  </si>
+  <si>
+    <t>Consumer lending — not Kevin's service</t>
+  </si>
+  <si>
+    <t>payday loans</t>
+  </si>
+  <si>
+    <t>Consumer lending</t>
+  </si>
+  <si>
+    <t>personal loan</t>
+  </si>
+  <si>
+    <t>Consumer lending — not B2B</t>
+  </si>
+  <si>
+    <t>personal loans</t>
+  </si>
+  <si>
+    <t>student loan</t>
+  </si>
+  <si>
+    <t>Education finance — not relevant</t>
+  </si>
+  <si>
+    <t>student loans</t>
+  </si>
+  <si>
+    <t>Education finance</t>
+  </si>
+  <si>
+    <t>car loan</t>
+  </si>
+  <si>
+    <t>Consumer auto — not relevant</t>
+  </si>
+  <si>
+    <t>auto loan</t>
+  </si>
+  <si>
+    <t>Consumer auto</t>
+  </si>
+  <si>
+    <t>home loan</t>
+  </si>
+  <si>
+    <t>Residential mortgage — not commercial</t>
+  </si>
+  <si>
+    <t>mortgage</t>
+  </si>
+  <si>
+    <t>Residential mortgage — not Kevin's advisory</t>
+  </si>
+  <si>
+    <t>credit card</t>
+  </si>
+  <si>
+    <t>Consumer product — not relevant</t>
+  </si>
+  <si>
+    <t>credit cards</t>
+  </si>
+  <si>
+    <t>Consumer product</t>
+  </si>
+  <si>
+    <t>insurance</t>
+  </si>
+  <si>
+    <t>Not an insurance product</t>
+  </si>
+  <si>
+    <t>free grant</t>
+  </si>
+  <si>
+    <t>Kevin is paid advisory — not a free grant source</t>
+  </si>
+  <si>
+    <t>free grants</t>
+  </si>
+  <si>
+    <t>Paid advisory service</t>
+  </si>
+  <si>
+    <t>government grant</t>
+  </si>
+  <si>
+    <t>Not a government body</t>
+  </si>
+  <si>
+    <t>government grants</t>
+  </si>
+  <si>
+    <t>government funding</t>
+  </si>
+  <si>
+    <t>Not a government programme</t>
+  </si>
+  <si>
+    <t>nonprofit</t>
+  </si>
+  <si>
+    <t>Commercial clients only</t>
+  </si>
+  <si>
+    <t>charity</t>
+  </si>
+  <si>
+    <t>Not a charity service</t>
+  </si>
+  <si>
+    <t>donation</t>
+  </si>
+  <si>
+    <t>Not donations</t>
+  </si>
+  <si>
+    <t>scholarship</t>
+  </si>
+  <si>
+    <t>Education — not relevant</t>
+  </si>
+  <si>
+    <t>scholarships</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>welfare</t>
+  </si>
+  <si>
+    <t>Social welfare — not relevant</t>
+  </si>
+  <si>
+    <t>benefits</t>
+  </si>
+  <si>
+    <t>Government benefits — not relevant</t>
+  </si>
+  <si>
+    <t>crowdfunding</t>
+  </si>
+  <si>
+    <t>Retail crowdfunding — not Kevin's model</t>
+  </si>
+  <si>
+    <t>kickstarter</t>
+  </si>
+  <si>
+    <t>Crowdfunding platform</t>
+  </si>
+  <si>
+    <t>gofundme</t>
+  </si>
+  <si>
+    <t>indiegogo</t>
+  </si>
+  <si>
+    <t>go fund me</t>
+  </si>
+  <si>
+    <t>Crowdfunding</t>
+  </si>
+  <si>
+    <t>bitcoin</t>
+  </si>
+  <si>
+    <t>Crypto — not Kevin's finance area</t>
+  </si>
+  <si>
+    <t>crypto</t>
+  </si>
+  <si>
+    <t>Speculative crypto assets</t>
+  </si>
+  <si>
+    <t>cryptocurrency</t>
+  </si>
+  <si>
+    <t>Speculative assets</t>
+  </si>
+  <si>
+    <t>ethereum</t>
+  </si>
+  <si>
+    <t>Crypto</t>
+  </si>
+  <si>
+    <t>nft</t>
+  </si>
+  <si>
+    <t>Non-fungible tokens — not relevant</t>
+  </si>
+  <si>
+    <t>forex trading</t>
+  </si>
+  <si>
+    <t>Retail FX trading — not advisory</t>
+  </si>
+  <si>
+    <t>day trading</t>
+  </si>
+  <si>
+    <t>Retail trading</t>
+  </si>
+  <si>
+    <t>stock trading</t>
+  </si>
+  <si>
+    <t>Retail equities — not relevant</t>
+  </si>
+  <si>
+    <t>penny stocks</t>
+  </si>
+  <si>
+    <t>Retail speculation</t>
+  </si>
+  <si>
+    <t>mlm</t>
+  </si>
+  <si>
+    <t>Multi-level marketing — not relevant</t>
+  </si>
+  <si>
+    <t>network marketing</t>
+  </si>
+  <si>
+    <t>MLM adjacent</t>
+  </si>
+  <si>
+    <t>pyramid scheme</t>
+  </si>
+  <si>
+    <t>Fraud adjacent — negative brand impact</t>
+  </si>
+  <si>
+    <t>make money online</t>
+  </si>
+  <si>
+    <t>Get-rich-quick — not Kevin's positioning</t>
+  </si>
+  <si>
+    <t>passive income</t>
+  </si>
+  <si>
+    <t>Not advisory</t>
+  </si>
+  <si>
+    <t>lottery</t>
+  </si>
+  <si>
+    <t>Gambling</t>
+  </si>
+  <si>
+    <t>casino</t>
+  </si>
+  <si>
+    <t>gambling</t>
+  </si>
+  <si>
+    <t>jobs</t>
+  </si>
+  <si>
+    <t>Employment seekers — not funders</t>
+  </si>
+  <si>
+    <t>salary</t>
+  </si>
+  <si>
+    <t>Employment context</t>
+  </si>
+  <si>
+    <t>hiring</t>
+  </si>
+  <si>
+    <t>Recruitment</t>
+  </si>
+  <si>
+    <t>recruitment</t>
+  </si>
+  <si>
+    <t>internship</t>
+  </si>
+  <si>
+    <t>Employment</t>
+  </si>
+  <si>
+    <t>volunteer</t>
+  </si>
+  <si>
+    <t>Not commercial</t>
+  </si>
+  <si>
+    <t>course</t>
+  </si>
+  <si>
+    <t>Education intent — low purchase intent</t>
+  </si>
+  <si>
+    <t>training</t>
+  </si>
+  <si>
+    <t>Education intent</t>
+  </si>
+  <si>
+    <t>certification</t>
+  </si>
+  <si>
+    <t>degree</t>
+  </si>
+  <si>
+    <t>Academic</t>
+  </si>
+  <si>
+    <t>university</t>
+  </si>
+  <si>
+    <t>what is</t>
+  </si>
+  <si>
+    <t>Informational — zero conversion intent</t>
+  </si>
+  <si>
+    <t>definition</t>
+  </si>
+  <si>
+    <t>Informational</t>
+  </si>
+  <si>
+    <t>meaning</t>
+  </si>
+  <si>
+    <t>wikipedia</t>
+  </si>
+  <si>
+    <t>Research — not buying intent</t>
+  </si>
+  <si>
+    <t>reddit</t>
+  </si>
+  <si>
+    <t>Forum research — not buying intent</t>
+  </si>
+  <si>
+    <t>youtube</t>
+  </si>
+  <si>
+    <t>Video — not buying intent</t>
+  </si>
+  <si>
+    <t>book</t>
+  </si>
+  <si>
+    <t>Publishing — not financial advisory</t>
+  </si>
+  <si>
+    <t>ebook</t>
+  </si>
+  <si>
+    <t>Publishing</t>
+  </si>
+  <si>
+    <t>template</t>
+  </si>
+  <si>
+    <t>Document template — not advisory</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>Research</t>
+  </si>
+  <si>
+    <t>sample</t>
+  </si>
+  <si>
+    <t>scam</t>
+  </si>
+  <si>
+    <t>Fraud research — negative brand context</t>
+  </si>
+  <si>
+    <t>legit</t>
+  </si>
+  <si>
+    <t>Trust research — waste spend</t>
+  </si>
+  <si>
+    <t>complaint</t>
+  </si>
+  <si>
+    <t>Complaint search</t>
+  </si>
+  <si>
+    <t>review</t>
+  </si>
+  <si>
+    <t>Review research without purchase intent</t>
+  </si>
+  <si>
+    <t>news</t>
+  </si>
+  <si>
+    <t>News intent — not converting</t>
+  </si>
+  <si>
+    <t>fake</t>
+  </si>
+  <si>
+    <t>Fraud concern</t>
+  </si>
+  <si>
+    <t>C1 - Core Project Finance — Campaign-Level Negatives</t>
+  </si>
+  <si>
+    <t>personal</t>
+  </si>
+  <si>
+    <t>Filters personal finance searches</t>
+  </si>
+  <si>
+    <t>micro finance</t>
+  </si>
+  <si>
+    <t>Kevin focuses on + deals</t>
+  </si>
+  <si>
+    <t>microfinance</t>
+  </si>
+  <si>
+    <t>Sub- deals — not Kevin's scope</t>
+  </si>
+  <si>
+    <t>small loan</t>
+  </si>
+  <si>
+    <t>Consumer / micro — not relevant</t>
+  </si>
+  <si>
+    <t>small loans</t>
+  </si>
+  <si>
+    <t>Consumer</t>
+  </si>
+  <si>
+    <t>consumer finance</t>
+  </si>
+  <si>
+    <t>B2C — not Kevin</t>
+  </si>
+  <si>
+    <t>retail finance</t>
+  </si>
+  <si>
+    <t>Consumer retail</t>
+  </si>
+  <si>
+    <t>wedding finance</t>
+  </si>
+  <si>
+    <t>Personal event — not commercial</t>
+  </si>
+  <si>
+    <t>holiday finance</t>
+  </si>
+  <si>
+    <t>Personal</t>
+  </si>
+  <si>
+    <t>vacation finance</t>
+  </si>
+  <si>
+    <t>car finance</t>
+  </si>
+  <si>
+    <t>vehicle finance</t>
+  </si>
+  <si>
+    <t>salary advance</t>
+  </si>
+  <si>
+    <t>Payroll advance — not relevant</t>
+  </si>
+  <si>
+    <t>C2 - Investor &amp; Capital Discovery — Campaign-Level Negatives</t>
+  </si>
+  <si>
+    <t>stock market</t>
+  </si>
+  <si>
+    <t>Retail equities — not project finance</t>
+  </si>
+  <si>
+    <t>stocks</t>
+  </si>
+  <si>
+    <t>Retail equities</t>
+  </si>
+  <si>
+    <t>shares</t>
+  </si>
+  <si>
+    <t>Retail stock shares</t>
+  </si>
+  <si>
+    <t>mutual fund</t>
+  </si>
+  <si>
+    <t>Retail fund product</t>
+  </si>
+  <si>
+    <t>mutual funds</t>
+  </si>
+  <si>
+    <t>etf</t>
+  </si>
+  <si>
+    <t>Exchange-traded fund — retail</t>
+  </si>
+  <si>
+    <t>pension</t>
+  </si>
+  <si>
+    <t>Retirement product</t>
+  </si>
+  <si>
+    <t>401k</t>
+  </si>
+  <si>
+    <t>US retirement account</t>
+  </si>
+  <si>
+    <t>isa</t>
+  </si>
+  <si>
+    <t>UK savings account — retail</t>
+  </si>
+  <si>
+    <t>angel list</t>
+  </si>
+  <si>
+    <t>AngelList platform — startup VC, not B2B project finance</t>
+  </si>
+  <si>
+    <t>crunchbase</t>
+  </si>
+  <si>
+    <t>Startup database — not project finance</t>
+  </si>
+  <si>
+    <t>shark tank</t>
+  </si>
+  <si>
+    <t>TV show — low quality traffic</t>
+  </si>
+  <si>
+    <t>dragons den</t>
+  </si>
+  <si>
+    <t>real estate agent</t>
+  </si>
+  <si>
+    <t>Property agent — not finance advisory</t>
+  </si>
+  <si>
+    <t>realtor</t>
+  </si>
+  <si>
+    <t>Property sales — not advisory</t>
+  </si>
+  <si>
+    <t>C3 - Apply / Get Funded — Campaign-Level Negatives</t>
+  </si>
+  <si>
+    <t>grant application</t>
+  </si>
+  <si>
+    <t>Free government grant — not Kevin's service</t>
+  </si>
+  <si>
+    <t>grant writing</t>
+  </si>
+  <si>
+    <t>Grant writer — different profession</t>
+  </si>
+  <si>
+    <t>grant writer</t>
+  </si>
+  <si>
+    <t>Different profession</t>
+  </si>
+  <si>
+    <t>free funding</t>
+  </si>
+  <si>
+    <t>Kevin's service is paid advisory</t>
+  </si>
+  <si>
+    <t>free business funding</t>
+  </si>
+  <si>
+    <t>Free — wrong expectation</t>
+  </si>
+  <si>
+    <t>nonprofit funding</t>
+  </si>
+  <si>
+    <t>Charities — not commercial clients</t>
+  </si>
+  <si>
+    <t>startup funding</t>
+  </si>
+  <si>
+    <t>Early-stage startups without revenue — below Kevin's threshold</t>
+  </si>
+  <si>
+    <t>seed funding</t>
+  </si>
+  <si>
+    <t>Pre-revenue — not Kevin's focus</t>
+  </si>
+  <si>
+    <t>seed round</t>
+  </si>
+  <si>
+    <t>VC startup — not project finance</t>
+  </si>
+  <si>
+    <t>pitch deck</t>
+  </si>
+  <si>
+    <t>Startup pitch — different service</t>
+  </si>
+  <si>
+    <t>pitch competition</t>
+  </si>
+  <si>
+    <t>Competition — not commercial</t>
+  </si>
+  <si>
+    <t>angel funding</t>
+  </si>
+  <si>
+    <t>Angel rounds — startup, not project finance</t>
+  </si>
+  <si>
+    <t>apply for benefits</t>
+  </si>
+  <si>
+    <t>apply for welfare</t>
+  </si>
+  <si>
+    <t>Government welfare</t>
+  </si>
+  <si>
+    <t>C4 - Africa &amp; Emerging Markets — Campaign-Level Negatives</t>
+  </si>
+  <si>
+    <t>safari</t>
+  </si>
+  <si>
+    <t>Tourism — not finance</t>
+  </si>
+  <si>
+    <t>tourism</t>
+  </si>
+  <si>
+    <t>Travel — not finance</t>
+  </si>
+  <si>
+    <t>travel</t>
+  </si>
+  <si>
+    <t>Travel context — not project finance</t>
+  </si>
+  <si>
+    <t>visa</t>
+  </si>
+  <si>
+    <t>Immigration visa — not financial advisory</t>
+  </si>
+  <si>
+    <t>immigration</t>
+  </si>
+  <si>
+    <t>Immigration service — not relevant</t>
+  </si>
+  <si>
+    <t>work permit</t>
+  </si>
+  <si>
+    <t>Immigration</t>
+  </si>
+  <si>
+    <t>study abroad</t>
+  </si>
+  <si>
+    <t>nigerian prince</t>
+  </si>
+  <si>
+    <t>Fraud association — brand risk</t>
+  </si>
+  <si>
+    <t>Nigerian fraud code — negative brand context</t>
+  </si>
+  <si>
+    <t>advance fee</t>
+  </si>
+  <si>
+    <t>Fraud type — brand risk</t>
+  </si>
+  <si>
+    <t>money transfer</t>
+  </si>
+  <si>
+    <t>Remittance — not project finance</t>
+  </si>
+  <si>
+    <t>send money</t>
+  </si>
+  <si>
+    <t>Remittance</t>
+  </si>
+  <si>
+    <t>remittance</t>
+  </si>
+  <si>
+    <t>Consumer money transfer</t>
+  </si>
+  <si>
+    <t>western union</t>
+  </si>
+  <si>
+    <t>Remittance provider</t>
+  </si>
+  <si>
+    <t>nollywood</t>
+  </si>
+  <si>
+    <t>Film industry — not finance</t>
+  </si>
+  <si>
+    <t>music</t>
+  </si>
+  <si>
+    <t>Entertainment — not finance</t>
+  </si>
+  <si>
+    <t>C5 - Sector-Specific Funding — Campaign-Level Negatives</t>
+  </si>
+  <si>
+    <t>buy a house</t>
+  </si>
+  <si>
+    <t>Residential property buyer — not commercial developer</t>
+  </si>
+  <si>
+    <t>buy house</t>
+  </si>
+  <si>
+    <t>Residential purchase</t>
+  </si>
+  <si>
+    <t>sell house</t>
+  </si>
+  <si>
+    <t>Residential sale</t>
+  </si>
+  <si>
+    <t>sell home</t>
+  </si>
+  <si>
+    <t>rent</t>
+  </si>
+  <si>
+    <t>Rental — not development finance</t>
+  </si>
+  <si>
+    <t>estate agent</t>
+  </si>
+  <si>
+    <t>Property sales agent — not finance</t>
+  </si>
+  <si>
+    <t>letting agent</t>
+  </si>
+  <si>
+    <t>Rental agent — not finance</t>
+  </si>
+  <si>
+    <t>conveyancing</t>
+  </si>
+  <si>
+    <t>Legal property transfer — not finance</t>
+  </si>
+  <si>
+    <t>house valuation</t>
+  </si>
+  <si>
+    <t>Property value — not project finance</t>
+  </si>
+  <si>
+    <t>hobby farm</t>
+  </si>
+  <si>
+    <t>Personal hobby — not commercial agri project</t>
+  </si>
+  <si>
+    <t>vegetable garden</t>
+  </si>
+  <si>
+    <t>Personal gardening</t>
+  </si>
+  <si>
+    <t>allotment</t>
+  </si>
+  <si>
+    <t>Personal gardening — UK</t>
+  </si>
+  <si>
+    <t>gardening</t>
+  </si>
+  <si>
+    <t>Personal hobby</t>
+  </si>
+  <si>
+    <t>organic food</t>
+  </si>
+  <si>
+    <t>Consumer food — not agri finance</t>
+  </si>
+  <si>
+    <t>fertilizer</t>
+  </si>
+  <si>
+    <t>Agricultural supply — not finance</t>
+  </si>
+  <si>
+    <t>seeds</t>
+  </si>
+  <si>
+    <t>Agricultural supply — not project finance</t>
+  </si>
+  <si>
+    <t>grocery</t>
+  </si>
+  <si>
+    <t>Consumer retail — not trade finance</t>
+  </si>
+  <si>
+    <t>shopping</t>
+  </si>
+  <si>
+    <t>Consumer — not B2B trade</t>
+  </si>
+  <si>
+    <t>retail shop</t>
+  </si>
+  <si>
+    <t>solar panels for home</t>
+  </si>
+  <si>
+    <t>Residential solar — not commercial project</t>
+  </si>
+  <si>
+    <t>home solar</t>
+  </si>
+  <si>
+    <t>Residential</t>
+  </si>
+  <si>
+    <t>green card</t>
+  </si>
+  <si>
+    <t>US immigration document — not green finance</t>
+  </si>
+  <si>
+    <t>recycling</t>
+  </si>
+  <si>
+    <t>Consumer activity — not project finance</t>
+  </si>
+  <si>
+    <t>pre-seed</t>
+  </si>
+  <si>
+    <t>Too early stage for Kevin</t>
+  </si>
+  <si>
+    <t>pre seed</t>
+  </si>
+  <si>
+    <t>Too early stage</t>
+  </si>
+  <si>
+    <t>incubator</t>
+  </si>
+  <si>
+    <t>Startup incubator — not project finance</t>
+  </si>
+  <si>
+    <t>accelerator</t>
+  </si>
+  <si>
+    <t>Startup accelerator — not project finance</t>
+  </si>
+  <si>
+    <t>y combinator</t>
+  </si>
+  <si>
+    <t>US startup accelerator — not Kevin's market</t>
   </si>
 </sst>
 </file>
@@ -1721,7 +2652,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1752,6 +2683,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF003C83"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA03070"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1765,7 +2708,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1776,6 +2719,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10857,4 +11805,2855 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B06CC7BD-2A97-4240-983A-0FBE3EBEED1E}">
+  <dimension ref="A1:E174"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.77734375" customWidth="1"/>
+    <col min="2" max="2" width="34.77734375" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" customWidth="1"/>
+    <col min="4" max="4" width="14.77734375" customWidth="1"/>
+    <col min="5" max="5" width="50.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B3" t="s">
+        <v>503</v>
+      </c>
+      <c r="C3" t="s">
+        <v>550</v>
+      </c>
+      <c r="D3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E3" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B4" t="s">
+        <v>503</v>
+      </c>
+      <c r="C4" t="s">
+        <v>552</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+      <c r="E4" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>464</v>
+      </c>
+      <c r="B5" t="s">
+        <v>503</v>
+      </c>
+      <c r="C5" t="s">
+        <v>554</v>
+      </c>
+      <c r="D5" t="s">
+        <v>367</v>
+      </c>
+      <c r="E5" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" t="s">
+        <v>503</v>
+      </c>
+      <c r="C6" t="s">
+        <v>556</v>
+      </c>
+      <c r="D6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>464</v>
+      </c>
+      <c r="B7" t="s">
+        <v>503</v>
+      </c>
+      <c r="C7" t="s">
+        <v>558</v>
+      </c>
+      <c r="D7" t="s">
+        <v>367</v>
+      </c>
+      <c r="E7" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>464</v>
+      </c>
+      <c r="B8" t="s">
+        <v>503</v>
+      </c>
+      <c r="C8" t="s">
+        <v>559</v>
+      </c>
+      <c r="D8" t="s">
+        <v>367</v>
+      </c>
+      <c r="E8" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>464</v>
+      </c>
+      <c r="B9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C9" t="s">
+        <v>561</v>
+      </c>
+      <c r="D9" t="s">
+        <v>367</v>
+      </c>
+      <c r="E9" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B10" t="s">
+        <v>503</v>
+      </c>
+      <c r="C10" t="s">
+        <v>563</v>
+      </c>
+      <c r="D10" t="s">
+        <v>367</v>
+      </c>
+      <c r="E10" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>464</v>
+      </c>
+      <c r="B11" t="s">
+        <v>503</v>
+      </c>
+      <c r="C11" t="s">
+        <v>565</v>
+      </c>
+      <c r="D11" t="s">
+        <v>367</v>
+      </c>
+      <c r="E11" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>464</v>
+      </c>
+      <c r="B12" t="s">
+        <v>503</v>
+      </c>
+      <c r="C12" t="s">
+        <v>567</v>
+      </c>
+      <c r="D12" t="s">
+        <v>367</v>
+      </c>
+      <c r="E12" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>464</v>
+      </c>
+      <c r="B13" t="s">
+        <v>503</v>
+      </c>
+      <c r="C13" t="s">
+        <v>569</v>
+      </c>
+      <c r="D13" t="s">
+        <v>386</v>
+      </c>
+      <c r="E13" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>464</v>
+      </c>
+      <c r="B14" t="s">
+        <v>503</v>
+      </c>
+      <c r="C14" t="s">
+        <v>571</v>
+      </c>
+      <c r="D14" t="s">
+        <v>367</v>
+      </c>
+      <c r="E14" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>464</v>
+      </c>
+      <c r="B15" t="s">
+        <v>503</v>
+      </c>
+      <c r="C15" t="s">
+        <v>573</v>
+      </c>
+      <c r="D15" t="s">
+        <v>367</v>
+      </c>
+      <c r="E15" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>464</v>
+      </c>
+      <c r="B16" t="s">
+        <v>503</v>
+      </c>
+      <c r="C16" t="s">
+        <v>575</v>
+      </c>
+      <c r="D16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E16" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>464</v>
+      </c>
+      <c r="B17" t="s">
+        <v>503</v>
+      </c>
+      <c r="C17" t="s">
+        <v>577</v>
+      </c>
+      <c r="D17" t="s">
+        <v>367</v>
+      </c>
+      <c r="E17" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>464</v>
+      </c>
+      <c r="B18" t="s">
+        <v>503</v>
+      </c>
+      <c r="C18" t="s">
+        <v>579</v>
+      </c>
+      <c r="D18" t="s">
+        <v>367</v>
+      </c>
+      <c r="E18" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>464</v>
+      </c>
+      <c r="B19" t="s">
+        <v>503</v>
+      </c>
+      <c r="C19" t="s">
+        <v>581</v>
+      </c>
+      <c r="D19" t="s">
+        <v>367</v>
+      </c>
+      <c r="E19" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>464</v>
+      </c>
+      <c r="B20" t="s">
+        <v>503</v>
+      </c>
+      <c r="C20" t="s">
+        <v>583</v>
+      </c>
+      <c r="D20" t="s">
+        <v>367</v>
+      </c>
+      <c r="E20" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>464</v>
+      </c>
+      <c r="B21" t="s">
+        <v>503</v>
+      </c>
+      <c r="C21" t="s">
+        <v>584</v>
+      </c>
+      <c r="D21" t="s">
+        <v>367</v>
+      </c>
+      <c r="E21" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>464</v>
+      </c>
+      <c r="B22" t="s">
+        <v>503</v>
+      </c>
+      <c r="C22" t="s">
+        <v>586</v>
+      </c>
+      <c r="D22" t="s">
+        <v>367</v>
+      </c>
+      <c r="E22" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>464</v>
+      </c>
+      <c r="B23" t="s">
+        <v>503</v>
+      </c>
+      <c r="C23" t="s">
+        <v>588</v>
+      </c>
+      <c r="D23" t="s">
+        <v>367</v>
+      </c>
+      <c r="E23" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>464</v>
+      </c>
+      <c r="B24" t="s">
+        <v>503</v>
+      </c>
+      <c r="C24" t="s">
+        <v>590</v>
+      </c>
+      <c r="D24" t="s">
+        <v>367</v>
+      </c>
+      <c r="E24" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>464</v>
+      </c>
+      <c r="B25" t="s">
+        <v>503</v>
+      </c>
+      <c r="C25" t="s">
+        <v>592</v>
+      </c>
+      <c r="D25" t="s">
+        <v>367</v>
+      </c>
+      <c r="E25" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>464</v>
+      </c>
+      <c r="B26" t="s">
+        <v>503</v>
+      </c>
+      <c r="C26" t="s">
+        <v>594</v>
+      </c>
+      <c r="D26" t="s">
+        <v>367</v>
+      </c>
+      <c r="E26" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>464</v>
+      </c>
+      <c r="B27" t="s">
+        <v>503</v>
+      </c>
+      <c r="C27" t="s">
+        <v>596</v>
+      </c>
+      <c r="D27" t="s">
+        <v>367</v>
+      </c>
+      <c r="E27" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>464</v>
+      </c>
+      <c r="B28" t="s">
+        <v>503</v>
+      </c>
+      <c r="C28" t="s">
+        <v>598</v>
+      </c>
+      <c r="D28" t="s">
+        <v>386</v>
+      </c>
+      <c r="E28" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>464</v>
+      </c>
+      <c r="B29" t="s">
+        <v>503</v>
+      </c>
+      <c r="C29" t="s">
+        <v>600</v>
+      </c>
+      <c r="D29" t="s">
+        <v>367</v>
+      </c>
+      <c r="E29" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>464</v>
+      </c>
+      <c r="B30" t="s">
+        <v>503</v>
+      </c>
+      <c r="C30" t="s">
+        <v>602</v>
+      </c>
+      <c r="D30" t="s">
+        <v>367</v>
+      </c>
+      <c r="E30" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>464</v>
+      </c>
+      <c r="B31" t="s">
+        <v>503</v>
+      </c>
+      <c r="C31" t="s">
+        <v>604</v>
+      </c>
+      <c r="D31" t="s">
+        <v>367</v>
+      </c>
+      <c r="E31" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>464</v>
+      </c>
+      <c r="B32" t="s">
+        <v>503</v>
+      </c>
+      <c r="C32" t="s">
+        <v>605</v>
+      </c>
+      <c r="D32" t="s">
+        <v>367</v>
+      </c>
+      <c r="E32" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>464</v>
+      </c>
+      <c r="B33" t="s">
+        <v>503</v>
+      </c>
+      <c r="C33" t="s">
+        <v>606</v>
+      </c>
+      <c r="D33" t="s">
+        <v>367</v>
+      </c>
+      <c r="E33" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>464</v>
+      </c>
+      <c r="B34" t="s">
+        <v>503</v>
+      </c>
+      <c r="C34" t="s">
+        <v>608</v>
+      </c>
+      <c r="D34" t="s">
+        <v>367</v>
+      </c>
+      <c r="E34" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>464</v>
+      </c>
+      <c r="B35" t="s">
+        <v>503</v>
+      </c>
+      <c r="C35" t="s">
+        <v>610</v>
+      </c>
+      <c r="D35" t="s">
+        <v>386</v>
+      </c>
+      <c r="E35" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>464</v>
+      </c>
+      <c r="B36" t="s">
+        <v>503</v>
+      </c>
+      <c r="C36" t="s">
+        <v>612</v>
+      </c>
+      <c r="D36" t="s">
+        <v>367</v>
+      </c>
+      <c r="E36" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>464</v>
+      </c>
+      <c r="B37" t="s">
+        <v>503</v>
+      </c>
+      <c r="C37" t="s">
+        <v>614</v>
+      </c>
+      <c r="D37" t="s">
+        <v>367</v>
+      </c>
+      <c r="E37" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>464</v>
+      </c>
+      <c r="B38" t="s">
+        <v>503</v>
+      </c>
+      <c r="C38" t="s">
+        <v>616</v>
+      </c>
+      <c r="D38" t="s">
+        <v>367</v>
+      </c>
+      <c r="E38" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>464</v>
+      </c>
+      <c r="B39" t="s">
+        <v>503</v>
+      </c>
+      <c r="C39" t="s">
+        <v>618</v>
+      </c>
+      <c r="D39" t="s">
+        <v>367</v>
+      </c>
+      <c r="E39" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>464</v>
+      </c>
+      <c r="B40" t="s">
+        <v>503</v>
+      </c>
+      <c r="C40" t="s">
+        <v>620</v>
+      </c>
+      <c r="D40" t="s">
+        <v>367</v>
+      </c>
+      <c r="E40" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>464</v>
+      </c>
+      <c r="B41" t="s">
+        <v>503</v>
+      </c>
+      <c r="C41" t="s">
+        <v>622</v>
+      </c>
+      <c r="D41" t="s">
+        <v>367</v>
+      </c>
+      <c r="E41" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>464</v>
+      </c>
+      <c r="B42" t="s">
+        <v>503</v>
+      </c>
+      <c r="C42" t="s">
+        <v>624</v>
+      </c>
+      <c r="D42" t="s">
+        <v>367</v>
+      </c>
+      <c r="E42" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>464</v>
+      </c>
+      <c r="B43" t="s">
+        <v>503</v>
+      </c>
+      <c r="C43" t="s">
+        <v>626</v>
+      </c>
+      <c r="D43" t="s">
+        <v>367</v>
+      </c>
+      <c r="E43" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>464</v>
+      </c>
+      <c r="B44" t="s">
+        <v>503</v>
+      </c>
+      <c r="C44" t="s">
+        <v>628</v>
+      </c>
+      <c r="D44" t="s">
+        <v>367</v>
+      </c>
+      <c r="E44" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>464</v>
+      </c>
+      <c r="B45" t="s">
+        <v>503</v>
+      </c>
+      <c r="C45" t="s">
+        <v>630</v>
+      </c>
+      <c r="D45" t="s">
+        <v>367</v>
+      </c>
+      <c r="E45" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>464</v>
+      </c>
+      <c r="B46" t="s">
+        <v>503</v>
+      </c>
+      <c r="C46" t="s">
+        <v>632</v>
+      </c>
+      <c r="D46" t="s">
+        <v>367</v>
+      </c>
+      <c r="E46" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>464</v>
+      </c>
+      <c r="B47" t="s">
+        <v>503</v>
+      </c>
+      <c r="C47" t="s">
+        <v>634</v>
+      </c>
+      <c r="D47" t="s">
+        <v>367</v>
+      </c>
+      <c r="E47" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>464</v>
+      </c>
+      <c r="B48" t="s">
+        <v>503</v>
+      </c>
+      <c r="C48" t="s">
+        <v>636</v>
+      </c>
+      <c r="D48" t="s">
+        <v>367</v>
+      </c>
+      <c r="E48" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>464</v>
+      </c>
+      <c r="B49" t="s">
+        <v>503</v>
+      </c>
+      <c r="C49" t="s">
+        <v>638</v>
+      </c>
+      <c r="D49" t="s">
+        <v>367</v>
+      </c>
+      <c r="E49" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>464</v>
+      </c>
+      <c r="B50" t="s">
+        <v>503</v>
+      </c>
+      <c r="C50" t="s">
+        <v>639</v>
+      </c>
+      <c r="D50" t="s">
+        <v>367</v>
+      </c>
+      <c r="E50" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>464</v>
+      </c>
+      <c r="B51" t="s">
+        <v>503</v>
+      </c>
+      <c r="C51" t="s">
+        <v>640</v>
+      </c>
+      <c r="D51" t="s">
+        <v>386</v>
+      </c>
+      <c r="E51" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>464</v>
+      </c>
+      <c r="B52" t="s">
+        <v>503</v>
+      </c>
+      <c r="C52" t="s">
+        <v>642</v>
+      </c>
+      <c r="D52" t="s">
+        <v>367</v>
+      </c>
+      <c r="E52" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>464</v>
+      </c>
+      <c r="B53" t="s">
+        <v>503</v>
+      </c>
+      <c r="C53" t="s">
+        <v>644</v>
+      </c>
+      <c r="D53" t="s">
+        <v>367</v>
+      </c>
+      <c r="E53" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>464</v>
+      </c>
+      <c r="B54" t="s">
+        <v>503</v>
+      </c>
+      <c r="C54" t="s">
+        <v>646</v>
+      </c>
+      <c r="D54" t="s">
+        <v>367</v>
+      </c>
+      <c r="E54" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>464</v>
+      </c>
+      <c r="B55" t="s">
+        <v>503</v>
+      </c>
+      <c r="C55" t="s">
+        <v>647</v>
+      </c>
+      <c r="D55" t="s">
+        <v>367</v>
+      </c>
+      <c r="E55" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>464</v>
+      </c>
+      <c r="B56" t="s">
+        <v>503</v>
+      </c>
+      <c r="C56" t="s">
+        <v>649</v>
+      </c>
+      <c r="D56" t="s">
+        <v>367</v>
+      </c>
+      <c r="E56" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>464</v>
+      </c>
+      <c r="B57" t="s">
+        <v>503</v>
+      </c>
+      <c r="C57" t="s">
+        <v>651</v>
+      </c>
+      <c r="D57" t="s">
+        <v>386</v>
+      </c>
+      <c r="E57" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>464</v>
+      </c>
+      <c r="B58" t="s">
+        <v>503</v>
+      </c>
+      <c r="C58" t="s">
+        <v>653</v>
+      </c>
+      <c r="D58" t="s">
+        <v>386</v>
+      </c>
+      <c r="E58" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>464</v>
+      </c>
+      <c r="B59" t="s">
+        <v>503</v>
+      </c>
+      <c r="C59" t="s">
+        <v>655</v>
+      </c>
+      <c r="D59" t="s">
+        <v>367</v>
+      </c>
+      <c r="E59" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>464</v>
+      </c>
+      <c r="B60" t="s">
+        <v>503</v>
+      </c>
+      <c r="C60" t="s">
+        <v>656</v>
+      </c>
+      <c r="D60" t="s">
+        <v>367</v>
+      </c>
+      <c r="E60" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>464</v>
+      </c>
+      <c r="B61" t="s">
+        <v>503</v>
+      </c>
+      <c r="C61" t="s">
+        <v>658</v>
+      </c>
+      <c r="D61" t="s">
+        <v>367</v>
+      </c>
+      <c r="E61" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>464</v>
+      </c>
+      <c r="B62" t="s">
+        <v>503</v>
+      </c>
+      <c r="C62" t="s">
+        <v>659</v>
+      </c>
+      <c r="D62" t="s">
+        <v>386</v>
+      </c>
+      <c r="E62" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>464</v>
+      </c>
+      <c r="B63" t="s">
+        <v>503</v>
+      </c>
+      <c r="C63" t="s">
+        <v>661</v>
+      </c>
+      <c r="D63" t="s">
+        <v>367</v>
+      </c>
+      <c r="E63" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>464</v>
+      </c>
+      <c r="B64" t="s">
+        <v>503</v>
+      </c>
+      <c r="C64" t="s">
+        <v>663</v>
+      </c>
+      <c r="D64" t="s">
+        <v>386</v>
+      </c>
+      <c r="E64" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>464</v>
+      </c>
+      <c r="B65" t="s">
+        <v>503</v>
+      </c>
+      <c r="C65" t="s">
+        <v>664</v>
+      </c>
+      <c r="D65" t="s">
+        <v>367</v>
+      </c>
+      <c r="E65" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>464</v>
+      </c>
+      <c r="B66" t="s">
+        <v>503</v>
+      </c>
+      <c r="C66" t="s">
+        <v>666</v>
+      </c>
+      <c r="D66" t="s">
+        <v>367</v>
+      </c>
+      <c r="E66" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>464</v>
+      </c>
+      <c r="B67" t="s">
+        <v>503</v>
+      </c>
+      <c r="C67" t="s">
+        <v>668</v>
+      </c>
+      <c r="D67" t="s">
+        <v>367</v>
+      </c>
+      <c r="E67" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>464</v>
+      </c>
+      <c r="B68" t="s">
+        <v>503</v>
+      </c>
+      <c r="C68" t="s">
+        <v>670</v>
+      </c>
+      <c r="D68" t="s">
+        <v>367</v>
+      </c>
+      <c r="E68" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>464</v>
+      </c>
+      <c r="B69" t="s">
+        <v>503</v>
+      </c>
+      <c r="C69" t="s">
+        <v>672</v>
+      </c>
+      <c r="D69" t="s">
+        <v>367</v>
+      </c>
+      <c r="E69" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>464</v>
+      </c>
+      <c r="B70" t="s">
+        <v>503</v>
+      </c>
+      <c r="C70" t="s">
+        <v>674</v>
+      </c>
+      <c r="D70" t="s">
+        <v>367</v>
+      </c>
+      <c r="E70" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>464</v>
+      </c>
+      <c r="B71" t="s">
+        <v>503</v>
+      </c>
+      <c r="C71" t="s">
+        <v>676</v>
+      </c>
+      <c r="D71" t="s">
+        <v>367</v>
+      </c>
+      <c r="E71" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>464</v>
+      </c>
+      <c r="B72" t="s">
+        <v>503</v>
+      </c>
+      <c r="C72" t="s">
+        <v>678</v>
+      </c>
+      <c r="D72" t="s">
+        <v>367</v>
+      </c>
+      <c r="E72" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>464</v>
+      </c>
+      <c r="B73" t="s">
+        <v>503</v>
+      </c>
+      <c r="C73" t="s">
+        <v>679</v>
+      </c>
+      <c r="D73" t="s">
+        <v>367</v>
+      </c>
+      <c r="E73" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>464</v>
+      </c>
+      <c r="B74" t="s">
+        <v>503</v>
+      </c>
+      <c r="C74" t="s">
+        <v>681</v>
+      </c>
+      <c r="D74" t="s">
+        <v>367</v>
+      </c>
+      <c r="E74" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>464</v>
+      </c>
+      <c r="B75" t="s">
+        <v>503</v>
+      </c>
+      <c r="C75" t="s">
+        <v>683</v>
+      </c>
+      <c r="D75" t="s">
+        <v>367</v>
+      </c>
+      <c r="E75" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>464</v>
+      </c>
+      <c r="B76" t="s">
+        <v>503</v>
+      </c>
+      <c r="C76" t="s">
+        <v>685</v>
+      </c>
+      <c r="D76" t="s">
+        <v>386</v>
+      </c>
+      <c r="E76" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>464</v>
+      </c>
+      <c r="B77" t="s">
+        <v>503</v>
+      </c>
+      <c r="C77" t="s">
+        <v>687</v>
+      </c>
+      <c r="D77" t="s">
+        <v>386</v>
+      </c>
+      <c r="E77" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>464</v>
+      </c>
+      <c r="B78" t="s">
+        <v>503</v>
+      </c>
+      <c r="C78" t="s">
+        <v>689</v>
+      </c>
+      <c r="D78" t="s">
+        <v>367</v>
+      </c>
+      <c r="E78" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>0</v>
+      </c>
+      <c r="B81" t="s">
+        <v>25</v>
+      </c>
+      <c r="C81" t="s">
+        <v>692</v>
+      </c>
+      <c r="D81" t="s">
+        <v>386</v>
+      </c>
+      <c r="E81" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" t="s">
+        <v>25</v>
+      </c>
+      <c r="C82" t="s">
+        <v>694</v>
+      </c>
+      <c r="D82" t="s">
+        <v>367</v>
+      </c>
+      <c r="E82" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>0</v>
+      </c>
+      <c r="B83" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" t="s">
+        <v>696</v>
+      </c>
+      <c r="D83" t="s">
+        <v>367</v>
+      </c>
+      <c r="E83" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>0</v>
+      </c>
+      <c r="B84" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" t="s">
+        <v>698</v>
+      </c>
+      <c r="D84" t="s">
+        <v>367</v>
+      </c>
+      <c r="E84" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>0</v>
+      </c>
+      <c r="B85" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" t="s">
+        <v>700</v>
+      </c>
+      <c r="D85" t="s">
+        <v>367</v>
+      </c>
+      <c r="E85" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>0</v>
+      </c>
+      <c r="B86" t="s">
+        <v>25</v>
+      </c>
+      <c r="C86" t="s">
+        <v>702</v>
+      </c>
+      <c r="D86" t="s">
+        <v>367</v>
+      </c>
+      <c r="E86" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>0</v>
+      </c>
+      <c r="B87" t="s">
+        <v>25</v>
+      </c>
+      <c r="C87" t="s">
+        <v>704</v>
+      </c>
+      <c r="D87" t="s">
+        <v>367</v>
+      </c>
+      <c r="E87" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>0</v>
+      </c>
+      <c r="B88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C88" t="s">
+        <v>706</v>
+      </c>
+      <c r="D88" t="s">
+        <v>367</v>
+      </c>
+      <c r="E88" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" t="s">
+        <v>25</v>
+      </c>
+      <c r="C89" t="s">
+        <v>708</v>
+      </c>
+      <c r="D89" t="s">
+        <v>367</v>
+      </c>
+      <c r="E89" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>0</v>
+      </c>
+      <c r="B90" t="s">
+        <v>25</v>
+      </c>
+      <c r="C90" t="s">
+        <v>710</v>
+      </c>
+      <c r="D90" t="s">
+        <v>367</v>
+      </c>
+      <c r="E90" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>0</v>
+      </c>
+      <c r="B91" t="s">
+        <v>25</v>
+      </c>
+      <c r="C91" t="s">
+        <v>711</v>
+      </c>
+      <c r="D91" t="s">
+        <v>367</v>
+      </c>
+      <c r="E91" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>0</v>
+      </c>
+      <c r="B92" t="s">
+        <v>25</v>
+      </c>
+      <c r="C92" t="s">
+        <v>712</v>
+      </c>
+      <c r="D92" t="s">
+        <v>367</v>
+      </c>
+      <c r="E92" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" t="s">
+        <v>25</v>
+      </c>
+      <c r="C93" t="s">
+        <v>713</v>
+      </c>
+      <c r="D93" t="s">
+        <v>367</v>
+      </c>
+      <c r="E93" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="B95" s="8"/>
+      <c r="C95" s="8"/>
+      <c r="D95" s="8"/>
+      <c r="E95" s="8"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" t="s">
+        <v>71</v>
+      </c>
+      <c r="C96" t="s">
+        <v>716</v>
+      </c>
+      <c r="D96" t="s">
+        <v>367</v>
+      </c>
+      <c r="E96" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>0</v>
+      </c>
+      <c r="B97" t="s">
+        <v>71</v>
+      </c>
+      <c r="C97" t="s">
+        <v>718</v>
+      </c>
+      <c r="D97" t="s">
+        <v>367</v>
+      </c>
+      <c r="E97" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>0</v>
+      </c>
+      <c r="B98" t="s">
+        <v>71</v>
+      </c>
+      <c r="C98" t="s">
+        <v>720</v>
+      </c>
+      <c r="D98" t="s">
+        <v>367</v>
+      </c>
+      <c r="E98" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>0</v>
+      </c>
+      <c r="B99" t="s">
+        <v>71</v>
+      </c>
+      <c r="C99" t="s">
+        <v>722</v>
+      </c>
+      <c r="D99" t="s">
+        <v>367</v>
+      </c>
+      <c r="E99" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>0</v>
+      </c>
+      <c r="B100" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100" t="s">
+        <v>724</v>
+      </c>
+      <c r="D100" t="s">
+        <v>367</v>
+      </c>
+      <c r="E100" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>0</v>
+      </c>
+      <c r="B101" t="s">
+        <v>71</v>
+      </c>
+      <c r="C101" t="s">
+        <v>725</v>
+      </c>
+      <c r="D101" t="s">
+        <v>367</v>
+      </c>
+      <c r="E101" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>0</v>
+      </c>
+      <c r="B102" t="s">
+        <v>71</v>
+      </c>
+      <c r="C102" t="s">
+        <v>727</v>
+      </c>
+      <c r="D102" t="s">
+        <v>367</v>
+      </c>
+      <c r="E102" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>0</v>
+      </c>
+      <c r="B103" t="s">
+        <v>71</v>
+      </c>
+      <c r="C103" t="s">
+        <v>729</v>
+      </c>
+      <c r="D103" t="s">
+        <v>367</v>
+      </c>
+      <c r="E103" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>0</v>
+      </c>
+      <c r="B104" t="s">
+        <v>71</v>
+      </c>
+      <c r="C104" t="s">
+        <v>731</v>
+      </c>
+      <c r="D104" t="s">
+        <v>367</v>
+      </c>
+      <c r="E104" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" t="s">
+        <v>0</v>
+      </c>
+      <c r="B105" t="s">
+        <v>71</v>
+      </c>
+      <c r="C105" t="s">
+        <v>733</v>
+      </c>
+      <c r="D105" t="s">
+        <v>367</v>
+      </c>
+      <c r="E105" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B106" t="s">
+        <v>71</v>
+      </c>
+      <c r="C106" t="s">
+        <v>735</v>
+      </c>
+      <c r="D106" t="s">
+        <v>367</v>
+      </c>
+      <c r="E106" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>0</v>
+      </c>
+      <c r="B107" t="s">
+        <v>71</v>
+      </c>
+      <c r="C107" t="s">
+        <v>737</v>
+      </c>
+      <c r="D107" t="s">
+        <v>367</v>
+      </c>
+      <c r="E107" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" t="s">
+        <v>71</v>
+      </c>
+      <c r="C108" t="s">
+        <v>739</v>
+      </c>
+      <c r="D108" t="s">
+        <v>367</v>
+      </c>
+      <c r="E108" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>0</v>
+      </c>
+      <c r="B109" t="s">
+        <v>71</v>
+      </c>
+      <c r="C109" t="s">
+        <v>740</v>
+      </c>
+      <c r="D109" t="s">
+        <v>367</v>
+      </c>
+      <c r="E109" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>0</v>
+      </c>
+      <c r="B110" t="s">
+        <v>71</v>
+      </c>
+      <c r="C110" t="s">
+        <v>742</v>
+      </c>
+      <c r="D110" t="s">
+        <v>367</v>
+      </c>
+      <c r="E110" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B112" s="9"/>
+      <c r="C112" s="9"/>
+      <c r="D112" s="9"/>
+      <c r="E112" s="9"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>0</v>
+      </c>
+      <c r="B113" t="s">
+        <v>159</v>
+      </c>
+      <c r="C113" t="s">
+        <v>745</v>
+      </c>
+      <c r="D113" t="s">
+        <v>367</v>
+      </c>
+      <c r="E113" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" t="s">
+        <v>159</v>
+      </c>
+      <c r="C114" t="s">
+        <v>747</v>
+      </c>
+      <c r="D114" t="s">
+        <v>367</v>
+      </c>
+      <c r="E114" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>0</v>
+      </c>
+      <c r="B115" t="s">
+        <v>159</v>
+      </c>
+      <c r="C115" t="s">
+        <v>749</v>
+      </c>
+      <c r="D115" t="s">
+        <v>367</v>
+      </c>
+      <c r="E115" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B116" t="s">
+        <v>159</v>
+      </c>
+      <c r="C116" t="s">
+        <v>751</v>
+      </c>
+      <c r="D116" t="s">
+        <v>367</v>
+      </c>
+      <c r="E116" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>0</v>
+      </c>
+      <c r="B117" t="s">
+        <v>159</v>
+      </c>
+      <c r="C117" t="s">
+        <v>753</v>
+      </c>
+      <c r="D117" t="s">
+        <v>367</v>
+      </c>
+      <c r="E117" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" t="s">
+        <v>0</v>
+      </c>
+      <c r="B118" t="s">
+        <v>159</v>
+      </c>
+      <c r="C118" t="s">
+        <v>755</v>
+      </c>
+      <c r="D118" t="s">
+        <v>367</v>
+      </c>
+      <c r="E118" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" t="s">
+        <v>0</v>
+      </c>
+      <c r="B119" t="s">
+        <v>159</v>
+      </c>
+      <c r="C119" t="s">
+        <v>757</v>
+      </c>
+      <c r="D119" t="s">
+        <v>386</v>
+      </c>
+      <c r="E119" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" t="s">
+        <v>0</v>
+      </c>
+      <c r="B120" t="s">
+        <v>159</v>
+      </c>
+      <c r="C120" t="s">
+        <v>759</v>
+      </c>
+      <c r="D120" t="s">
+        <v>367</v>
+      </c>
+      <c r="E120" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" t="s">
+        <v>0</v>
+      </c>
+      <c r="B121" t="s">
+        <v>159</v>
+      </c>
+      <c r="C121" t="s">
+        <v>761</v>
+      </c>
+      <c r="D121" t="s">
+        <v>367</v>
+      </c>
+      <c r="E121" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" t="s">
+        <v>0</v>
+      </c>
+      <c r="B122" t="s">
+        <v>159</v>
+      </c>
+      <c r="C122" t="s">
+        <v>763</v>
+      </c>
+      <c r="D122" t="s">
+        <v>367</v>
+      </c>
+      <c r="E122" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>0</v>
+      </c>
+      <c r="B123" t="s">
+        <v>159</v>
+      </c>
+      <c r="C123" t="s">
+        <v>765</v>
+      </c>
+      <c r="D123" t="s">
+        <v>367</v>
+      </c>
+      <c r="E123" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>0</v>
+      </c>
+      <c r="B124" t="s">
+        <v>159</v>
+      </c>
+      <c r="C124" t="s">
+        <v>767</v>
+      </c>
+      <c r="D124" t="s">
+        <v>367</v>
+      </c>
+      <c r="E124" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" t="s">
+        <v>159</v>
+      </c>
+      <c r="C125" t="s">
+        <v>769</v>
+      </c>
+      <c r="D125" t="s">
+        <v>367</v>
+      </c>
+      <c r="E125" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>0</v>
+      </c>
+      <c r="B126" t="s">
+        <v>159</v>
+      </c>
+      <c r="C126" t="s">
+        <v>770</v>
+      </c>
+      <c r="D126" t="s">
+        <v>367</v>
+      </c>
+      <c r="E126" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="B128" s="6"/>
+      <c r="C128" s="6"/>
+      <c r="D128" s="6"/>
+      <c r="E128" s="6"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>0</v>
+      </c>
+      <c r="B129" t="s">
+        <v>223</v>
+      </c>
+      <c r="C129" t="s">
+        <v>773</v>
+      </c>
+      <c r="D129" t="s">
+        <v>367</v>
+      </c>
+      <c r="E129" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>0</v>
+      </c>
+      <c r="B130" t="s">
+        <v>223</v>
+      </c>
+      <c r="C130" t="s">
+        <v>775</v>
+      </c>
+      <c r="D130" t="s">
+        <v>367</v>
+      </c>
+      <c r="E130" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>0</v>
+      </c>
+      <c r="B131" t="s">
+        <v>223</v>
+      </c>
+      <c r="C131" t="s">
+        <v>777</v>
+      </c>
+      <c r="D131" t="s">
+        <v>386</v>
+      </c>
+      <c r="E131" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>0</v>
+      </c>
+      <c r="B132" t="s">
+        <v>223</v>
+      </c>
+      <c r="C132" t="s">
+        <v>779</v>
+      </c>
+      <c r="D132" t="s">
+        <v>386</v>
+      </c>
+      <c r="E132" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>0</v>
+      </c>
+      <c r="B133" t="s">
+        <v>223</v>
+      </c>
+      <c r="C133" t="s">
+        <v>781</v>
+      </c>
+      <c r="D133" t="s">
+        <v>367</v>
+      </c>
+      <c r="E133" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>0</v>
+      </c>
+      <c r="B134" t="s">
+        <v>223</v>
+      </c>
+      <c r="C134" t="s">
+        <v>783</v>
+      </c>
+      <c r="D134" t="s">
+        <v>367</v>
+      </c>
+      <c r="E134" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
+        <v>0</v>
+      </c>
+      <c r="B135" t="s">
+        <v>223</v>
+      </c>
+      <c r="C135" t="s">
+        <v>785</v>
+      </c>
+      <c r="D135" t="s">
+        <v>367</v>
+      </c>
+      <c r="E135" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" t="s">
+        <v>0</v>
+      </c>
+      <c r="B136" t="s">
+        <v>223</v>
+      </c>
+      <c r="C136" t="s">
+        <v>786</v>
+      </c>
+      <c r="D136" t="s">
+        <v>367</v>
+      </c>
+      <c r="E136" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" t="s">
+        <v>223</v>
+      </c>
+      <c r="C137">
+        <v>419</v>
+      </c>
+      <c r="D137" t="s">
+        <v>367</v>
+      </c>
+      <c r="E137" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" t="s">
+        <v>0</v>
+      </c>
+      <c r="B138" t="s">
+        <v>223</v>
+      </c>
+      <c r="C138" t="s">
+        <v>789</v>
+      </c>
+      <c r="D138" t="s">
+        <v>367</v>
+      </c>
+      <c r="E138" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B139" t="s">
+        <v>223</v>
+      </c>
+      <c r="C139" t="s">
+        <v>791</v>
+      </c>
+      <c r="D139" t="s">
+        <v>367</v>
+      </c>
+      <c r="E139" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" t="s">
+        <v>0</v>
+      </c>
+      <c r="B140" t="s">
+        <v>223</v>
+      </c>
+      <c r="C140" t="s">
+        <v>793</v>
+      </c>
+      <c r="D140" t="s">
+        <v>367</v>
+      </c>
+      <c r="E140" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" t="s">
+        <v>0</v>
+      </c>
+      <c r="B141" t="s">
+        <v>223</v>
+      </c>
+      <c r="C141" t="s">
+        <v>795</v>
+      </c>
+      <c r="D141" t="s">
+        <v>367</v>
+      </c>
+      <c r="E141" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>0</v>
+      </c>
+      <c r="B142" t="s">
+        <v>223</v>
+      </c>
+      <c r="C142" t="s">
+        <v>797</v>
+      </c>
+      <c r="D142" t="s">
+        <v>367</v>
+      </c>
+      <c r="E142" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>0</v>
+      </c>
+      <c r="B143" t="s">
+        <v>223</v>
+      </c>
+      <c r="C143" t="s">
+        <v>799</v>
+      </c>
+      <c r="D143" t="s">
+        <v>367</v>
+      </c>
+      <c r="E143" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>0</v>
+      </c>
+      <c r="B144" t="s">
+        <v>223</v>
+      </c>
+      <c r="C144" t="s">
+        <v>801</v>
+      </c>
+      <c r="D144" t="s">
+        <v>386</v>
+      </c>
+      <c r="E144" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="10" t="s">
+        <v>803</v>
+      </c>
+      <c r="B146" s="10"/>
+      <c r="C146" s="10"/>
+      <c r="D146" s="10"/>
+      <c r="E146" s="10"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" t="s">
+        <v>266</v>
+      </c>
+      <c r="C147" t="s">
+        <v>804</v>
+      </c>
+      <c r="D147" t="s">
+        <v>367</v>
+      </c>
+      <c r="E147" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" t="s">
+        <v>266</v>
+      </c>
+      <c r="C148" t="s">
+        <v>806</v>
+      </c>
+      <c r="D148" t="s">
+        <v>367</v>
+      </c>
+      <c r="E148" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>0</v>
+      </c>
+      <c r="B149" t="s">
+        <v>266</v>
+      </c>
+      <c r="C149" t="s">
+        <v>808</v>
+      </c>
+      <c r="D149" t="s">
+        <v>367</v>
+      </c>
+      <c r="E149" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>0</v>
+      </c>
+      <c r="B150" t="s">
+        <v>266</v>
+      </c>
+      <c r="C150" t="s">
+        <v>810</v>
+      </c>
+      <c r="D150" t="s">
+        <v>367</v>
+      </c>
+      <c r="E150" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>0</v>
+      </c>
+      <c r="B151" t="s">
+        <v>266</v>
+      </c>
+      <c r="C151" t="s">
+        <v>811</v>
+      </c>
+      <c r="D151" t="s">
+        <v>386</v>
+      </c>
+      <c r="E151" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>0</v>
+      </c>
+      <c r="B152" t="s">
+        <v>266</v>
+      </c>
+      <c r="C152" t="s">
+        <v>813</v>
+      </c>
+      <c r="D152" t="s">
+        <v>367</v>
+      </c>
+      <c r="E152" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>0</v>
+      </c>
+      <c r="B153" t="s">
+        <v>266</v>
+      </c>
+      <c r="C153" t="s">
+        <v>815</v>
+      </c>
+      <c r="D153" t="s">
+        <v>367</v>
+      </c>
+      <c r="E153" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>0</v>
+      </c>
+      <c r="B154" t="s">
+        <v>266</v>
+      </c>
+      <c r="C154" t="s">
+        <v>817</v>
+      </c>
+      <c r="D154" t="s">
+        <v>367</v>
+      </c>
+      <c r="E154" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>0</v>
+      </c>
+      <c r="B155" t="s">
+        <v>266</v>
+      </c>
+      <c r="C155" t="s">
+        <v>819</v>
+      </c>
+      <c r="D155" t="s">
+        <v>367</v>
+      </c>
+      <c r="E155" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>0</v>
+      </c>
+      <c r="B156" t="s">
+        <v>266</v>
+      </c>
+      <c r="C156" t="s">
+        <v>821</v>
+      </c>
+      <c r="D156" t="s">
+        <v>367</v>
+      </c>
+      <c r="E156" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>0</v>
+      </c>
+      <c r="B157" t="s">
+        <v>266</v>
+      </c>
+      <c r="C157" t="s">
+        <v>823</v>
+      </c>
+      <c r="D157" t="s">
+        <v>367</v>
+      </c>
+      <c r="E157" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" t="s">
+        <v>266</v>
+      </c>
+      <c r="C158" t="s">
+        <v>825</v>
+      </c>
+      <c r="D158" t="s">
+        <v>367</v>
+      </c>
+      <c r="E158" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>0</v>
+      </c>
+      <c r="B159" t="s">
+        <v>266</v>
+      </c>
+      <c r="C159" t="s">
+        <v>827</v>
+      </c>
+      <c r="D159" t="s">
+        <v>367</v>
+      </c>
+      <c r="E159" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>0</v>
+      </c>
+      <c r="B160" t="s">
+        <v>266</v>
+      </c>
+      <c r="C160" t="s">
+        <v>829</v>
+      </c>
+      <c r="D160" t="s">
+        <v>367</v>
+      </c>
+      <c r="E160" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>0</v>
+      </c>
+      <c r="B161" t="s">
+        <v>266</v>
+      </c>
+      <c r="C161" t="s">
+        <v>831</v>
+      </c>
+      <c r="D161" t="s">
+        <v>367</v>
+      </c>
+      <c r="E161" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>0</v>
+      </c>
+      <c r="B162" t="s">
+        <v>266</v>
+      </c>
+      <c r="C162" t="s">
+        <v>833</v>
+      </c>
+      <c r="D162" t="s">
+        <v>386</v>
+      </c>
+      <c r="E162" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>0</v>
+      </c>
+      <c r="B163" t="s">
+        <v>266</v>
+      </c>
+      <c r="C163" t="s">
+        <v>835</v>
+      </c>
+      <c r="D163" t="s">
+        <v>367</v>
+      </c>
+      <c r="E163" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>0</v>
+      </c>
+      <c r="B164" t="s">
+        <v>266</v>
+      </c>
+      <c r="C164" t="s">
+        <v>837</v>
+      </c>
+      <c r="D164" t="s">
+        <v>367</v>
+      </c>
+      <c r="E164" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>0</v>
+      </c>
+      <c r="B165" t="s">
+        <v>266</v>
+      </c>
+      <c r="C165" t="s">
+        <v>839</v>
+      </c>
+      <c r="D165" t="s">
+        <v>367</v>
+      </c>
+      <c r="E165" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>0</v>
+      </c>
+      <c r="B166" t="s">
+        <v>266</v>
+      </c>
+      <c r="C166" t="s">
+        <v>840</v>
+      </c>
+      <c r="D166" t="s">
+        <v>367</v>
+      </c>
+      <c r="E166" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>0</v>
+      </c>
+      <c r="B167" t="s">
+        <v>266</v>
+      </c>
+      <c r="C167" t="s">
+        <v>842</v>
+      </c>
+      <c r="D167" t="s">
+        <v>367</v>
+      </c>
+      <c r="E167" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" t="s">
+        <v>266</v>
+      </c>
+      <c r="C168" t="s">
+        <v>844</v>
+      </c>
+      <c r="D168" t="s">
+        <v>367</v>
+      </c>
+      <c r="E168" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>0</v>
+      </c>
+      <c r="B169" t="s">
+        <v>266</v>
+      </c>
+      <c r="C169" t="s">
+        <v>846</v>
+      </c>
+      <c r="D169" t="s">
+        <v>367</v>
+      </c>
+      <c r="E169" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s">
+        <v>266</v>
+      </c>
+      <c r="C170" t="s">
+        <v>848</v>
+      </c>
+      <c r="D170" t="s">
+        <v>367</v>
+      </c>
+      <c r="E170" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>0</v>
+      </c>
+      <c r="B171" t="s">
+        <v>266</v>
+      </c>
+      <c r="C171" t="s">
+        <v>850</v>
+      </c>
+      <c r="D171" t="s">
+        <v>367</v>
+      </c>
+      <c r="E171" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" t="s">
+        <v>266</v>
+      </c>
+      <c r="C172" t="s">
+        <v>852</v>
+      </c>
+      <c r="D172" t="s">
+        <v>367</v>
+      </c>
+      <c r="E172" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" t="s">
+        <v>0</v>
+      </c>
+      <c r="B173" t="s">
+        <v>266</v>
+      </c>
+      <c r="C173" t="s">
+        <v>854</v>
+      </c>
+      <c r="D173" t="s">
+        <v>367</v>
+      </c>
+      <c r="E173" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" t="s">
+        <v>0</v>
+      </c>
+      <c r="B174" t="s">
+        <v>266</v>
+      </c>
+      <c r="C174" t="s">
+        <v>856</v>
+      </c>
+      <c r="D174" t="s">
+        <v>367</v>
+      </c>
+      <c r="E174" t="s">
+        <v>857</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A80:E80"/>
+    <mergeCell ref="A95:E95"/>
+    <mergeCell ref="A112:E112"/>
+    <mergeCell ref="A128:E128"/>
+    <mergeCell ref="A146:E146"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Google_Ads_Campaign_1.xlsx
+++ b/Google_Ads_Campaign_1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="e:\react project\kevin-graham-profile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\react project\kevin-graham-profile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB412D83-9484-43BD-A383-2A638163F178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF55C9B7-E31E-445F-865F-4E86128ACDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" firstSheet="3" activeTab="6" xr2:uid="{D76E1C49-027D-4506-86F0-0DA797BAD358}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{D76E1C49-027D-4506-86F0-0DA797BAD358}"/>
   </bookViews>
   <sheets>
     <sheet name="Google Ads Upload" sheetId="1" r:id="rId1"/>
@@ -2620,7 +2620,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2647,6 +2647,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF235637"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -2705,10 +2713,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2719,13 +2728,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -4116,7 +4127,7 @@
       <c r="V14" t="s">
         <v>307</v>
       </c>
-      <c r="W14" t="s">
+      <c r="W14" s="11" t="s">
         <v>47</v>
       </c>
       <c r="X14" t="s">
@@ -4204,8 +4215,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="W14" r:id="rId1" xr:uid="{0E7D9C30-2918-4FE9-8C16-3A8954B0142B}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -11837,13 +11851,13 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>549</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -13138,13 +13152,13 @@
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="7" t="s">
+      <c r="A80" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="8"/>
+      <c r="E80" s="8"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
@@ -13368,13 +13382,13 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="9" t="s">
         <v>715</v>
       </c>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
-      <c r="D95" s="8"/>
-      <c r="E95" s="8"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
@@ -13632,13 +13646,13 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="9" t="s">
+      <c r="A112" s="10" t="s">
         <v>744</v>
       </c>
-      <c r="B112" s="9"/>
-      <c r="C112" s="9"/>
-      <c r="D112" s="9"/>
-      <c r="E112" s="9"/>
+      <c r="B112" s="10"/>
+      <c r="C112" s="10"/>
+      <c r="D112" s="10"/>
+      <c r="E112" s="10"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
@@ -13879,13 +13893,13 @@
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="6" t="s">
+      <c r="A128" s="7" t="s">
         <v>772</v>
       </c>
-      <c r="B128" s="6"/>
-      <c r="C128" s="6"/>
-      <c r="D128" s="6"/>
-      <c r="E128" s="6"/>
+      <c r="B128" s="7"/>
+      <c r="C128" s="7"/>
+      <c r="D128" s="7"/>
+      <c r="E128" s="7"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
@@ -14160,13 +14174,13 @@
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="10" t="s">
+      <c r="A146" s="6" t="s">
         <v>803</v>
       </c>
-      <c r="B146" s="10"/>
-      <c r="C146" s="10"/>
-      <c r="D146" s="10"/>
-      <c r="E146" s="10"/>
+      <c r="B146" s="6"/>
+      <c r="C146" s="6"/>
+      <c r="D146" s="6"/>
+      <c r="E146" s="6"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
@@ -14646,12 +14660,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A146:E146"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A80:E80"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A112:E112"/>
     <mergeCell ref="A128:E128"/>
-    <mergeCell ref="A146:E146"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
